--- a/produtos1.xlsx
+++ b/produtos1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\catalogo_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21C6068-80A9-4B7E-8F7F-516D20BD7937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C55205D-AF5A-40C1-AD6C-B4FE2B9F3F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{02E3CDAF-A272-443C-8687-B38AE8A4CCA2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>Descrição</t>
   </si>
@@ -45,39 +45,12 @@
     <t>Preço Promoção</t>
   </si>
   <si>
-    <t>12.0062</t>
-  </si>
-  <si>
-    <t>70.0011</t>
-  </si>
-  <si>
-    <t>46.0042</t>
-  </si>
-  <si>
-    <t>15.0121</t>
-  </si>
-  <si>
-    <t>44.0010</t>
-  </si>
-  <si>
-    <t>04.0120</t>
-  </si>
-  <si>
-    <t>03.0099</t>
-  </si>
-  <si>
-    <t>07.0087</t>
-  </si>
-  <si>
     <t>15.0124</t>
   </si>
   <si>
     <t>04.0062</t>
   </si>
   <si>
-    <t>04.0212</t>
-  </si>
-  <si>
     <t>23.0130</t>
   </si>
   <si>
@@ -90,45 +63,12 @@
     <t>23.0128</t>
   </si>
   <si>
-    <t>23.0127</t>
-  </si>
-  <si>
-    <t>04.0135</t>
-  </si>
-  <si>
-    <t>KIT 2X9 SHIMANO ALIVIO   FREIO HIDRAULICO MT200 - CUBO 32F</t>
-  </si>
-  <si>
-    <t>LIMPEZA GERAL SOLIFES 500ML</t>
-  </si>
-  <si>
-    <t>PATINS MTB VB CH10 POWER 70MM</t>
-  </si>
-  <si>
-    <t>RODA LIVRE 20D COMANDER</t>
-  </si>
-  <si>
-    <t>GARFO 26 S. 21.1 MODE PTO</t>
-  </si>
-  <si>
-    <t>SELIM BEACH 2M INVIKTUS PTO C/ REFLETOR</t>
-  </si>
-  <si>
-    <t>CAMARA 26 BUTIL BISON (CAIXA FECHADA)</t>
-  </si>
-  <si>
-    <t>PASTILHA REFIL GTS QUAD. C/MOLA F DISCO PAR (GRANEL)</t>
-  </si>
-  <si>
     <t>RODA LIVRE 7V INDEX FALCON 14/28 BRONZE</t>
   </si>
   <si>
     <t>SELIM MTB VAZ INVIKTUS PTO</t>
   </si>
   <si>
-    <t>SELIM MTB VAZ GTS HY-298 NEO PTO</t>
-  </si>
-  <si>
     <t>MANOPLA FREERIDE MOOVE VERMELHO 165MM C/ FLANGE</t>
   </si>
   <si>
@@ -141,40 +81,277 @@
     <t>MANOPLA FREERIDE MOOVE LARANJA 165MM C/ FLANGE</t>
   </si>
   <si>
-    <t>MANOPLA FREERIDE MOOVE ROSA 165MM C/ FLANGE</t>
-  </si>
-  <si>
-    <t>SELIM SRX HAVAC VAZ R CICLO PTO</t>
-  </si>
-  <si>
-    <t>20.0115</t>
-  </si>
-  <si>
-    <t>21.0115</t>
-  </si>
-  <si>
-    <t>44.0734</t>
-  </si>
-  <si>
-    <t>46.0054</t>
-  </si>
-  <si>
-    <t>PEDIV 165MM R CICLO CROM (CX FECHADA)</t>
-  </si>
-  <si>
-    <t>CUBO D/T AL ROLLER VIPER PTO (CX FECHADA)</t>
-  </si>
-  <si>
-    <t>GARFO 29 S. AH SET ACO TAIWAN PTO (CX FECHADA)</t>
-  </si>
-  <si>
-    <t>PATINS MTB VB ORBITAL 70MM GTS (BLISTER) - (100 PARES)</t>
+    <t>03.0073</t>
+  </si>
+  <si>
+    <t>46.0045</t>
+  </si>
+  <si>
+    <t>01.0052</t>
+  </si>
+  <si>
+    <t>18.0029</t>
+  </si>
+  <si>
+    <t>22.0054</t>
+  </si>
+  <si>
+    <t>20.0001</t>
+  </si>
+  <si>
+    <t>23.0001</t>
+  </si>
+  <si>
+    <t>46.0003</t>
+  </si>
+  <si>
+    <t>10.0009</t>
+  </si>
+  <si>
+    <t>24.0042</t>
+  </si>
+  <si>
+    <t>39.0036</t>
+  </si>
+  <si>
+    <t>23.0102</t>
+  </si>
+  <si>
+    <t>23.0106</t>
+  </si>
+  <si>
+    <t>22.0090</t>
+  </si>
+  <si>
+    <t>57.0006</t>
+  </si>
+  <si>
+    <t>14.0012</t>
+  </si>
+  <si>
+    <t>09.0133</t>
+  </si>
+  <si>
+    <t>23.0045</t>
+  </si>
+  <si>
+    <t>08.0003</t>
+  </si>
+  <si>
+    <t>14.0021</t>
+  </si>
+  <si>
+    <t>40.0314</t>
+  </si>
+  <si>
+    <t>42.0004</t>
+  </si>
+  <si>
+    <t>20.0108</t>
+  </si>
+  <si>
+    <t>53.0025</t>
+  </si>
+  <si>
+    <t>52.0016</t>
+  </si>
+  <si>
+    <t>01.0238</t>
+  </si>
+  <si>
+    <t>04.0014</t>
+  </si>
+  <si>
+    <t>22.0080</t>
+  </si>
+  <si>
+    <t>01.0149</t>
+  </si>
+  <si>
+    <t>20.0089</t>
+  </si>
+  <si>
+    <t>04.0070</t>
+  </si>
+  <si>
+    <t>21.0104</t>
+  </si>
+  <si>
+    <t>78.0002</t>
+  </si>
+  <si>
+    <t>10.0121</t>
+  </si>
+  <si>
+    <t>23.0133</t>
+  </si>
+  <si>
+    <t>08.0011</t>
+  </si>
+  <si>
+    <t>22.0073</t>
+  </si>
+  <si>
+    <t>23.0050</t>
+  </si>
+  <si>
+    <t>21.0027</t>
+  </si>
+  <si>
+    <t>23.0132</t>
+  </si>
+  <si>
+    <t>32.0019</t>
+  </si>
+  <si>
+    <t>32.0021</t>
+  </si>
+  <si>
+    <t>04.0198</t>
+  </si>
+  <si>
+    <t>04.0202</t>
+  </si>
+  <si>
+    <t>CAMARA 26 BUTIL BISON</t>
+  </si>
+  <si>
+    <t>PATINS MTB PINO TAIWAN 60MM (10 PRS) PINO CENTRAL</t>
+  </si>
+  <si>
+    <t>PNEU 29X2.10 SRI PTO</t>
+  </si>
+  <si>
+    <t>CORRENTE GROSSA CY 114 ELLOS</t>
+  </si>
+  <si>
+    <t>MOV CENTRAL 45MM YAMADA ZINC</t>
+  </si>
+  <si>
+    <t>PEDIV 165MM R CICLO CROM</t>
+  </si>
+  <si>
+    <t>MANOPLA TIPO DIPLOMATA PRETO</t>
+  </si>
+  <si>
+    <t>PATINS MTB VB ORBITAL TAIWAN 70MM (10 PRS)</t>
+  </si>
+  <si>
+    <t>PEDAL 1/2 PLAT. FREE SPORT S/ESFERA PTO</t>
+  </si>
+  <si>
+    <t>CANOTE AL 27.2X350MM C/ CAR ADX PTO</t>
+  </si>
+  <si>
+    <t>BOMBA MINI PUMP AL GTS MTB/SPEED C/TRAVA E SUP</t>
+  </si>
+  <si>
+    <t>MANOPLA MTB GTA PTO/VM</t>
+  </si>
+  <si>
+    <t>MANOPLA MTB GTA PTO/AZ</t>
+  </si>
+  <si>
+    <t>MOV DIRECAO STD SUNDOW HP PTO - 9206</t>
+  </si>
+  <si>
+    <t>PARAFUSO P/ SELIM C/ TRAVA CISER (10 UN)</t>
+  </si>
+  <si>
+    <t>CAMBIO TRAS 6V S/G YAMADA PTO</t>
+  </si>
+  <si>
+    <t>GUIDAO 16 DH MTB TAIWAN PTO</t>
+  </si>
+  <si>
+    <t>MANOPLA MIRIM PTO</t>
+  </si>
+  <si>
+    <t>DESCANSO 26 ACO LATERAL T-SUECO</t>
+  </si>
+  <si>
+    <t>CAMBIO DIANT 31.8 SHIMANO TZ-510 (P.C)</t>
+  </si>
+  <si>
+    <t>BUZINA PATO SORTIDA (UNIDADE)</t>
+  </si>
+  <si>
+    <t>ESFERA TRAS 1/4 LINIERS (500UN)</t>
+  </si>
+  <si>
+    <t>PEDIV SINGLE AL GTA 34D P.QUAD CAMALEÃO</t>
+  </si>
+  <si>
+    <t>CADEADO 15MMX1200M ACO INVIKTUS PTO C/ CHAVE</t>
+  </si>
+  <si>
+    <t>RAIO 255X2.0MM INOX SHADDAR</t>
+  </si>
+  <si>
+    <t>PNEU 26X2.10 CINBORG PARRUDO FOX</t>
+  </si>
+  <si>
+    <t>SELIM SELLE ROYAL MIRIM KID PU C/ CARRINHO</t>
+  </si>
+  <si>
+    <t>MOV CENTRAL 34.7 KENLI S/ EIXO (5PCS)</t>
+  </si>
+  <si>
+    <t>PNEU 26X1.95 CINBORG ADVENTURE</t>
+  </si>
+  <si>
+    <t>PEDIV 115MM R CICLO CROM</t>
+  </si>
+  <si>
+    <t>SELIM ESSENZA ATHLETIC R CICLO S/CAR VNZ/CZ</t>
+  </si>
+  <si>
+    <t>CUBO K7 36F VIPER ROLLER DISC 6 PAWLS PRETO C/BLOC</t>
+  </si>
+  <si>
+    <t>CARRINHO DE SELIM BINGO ZINC</t>
+  </si>
+  <si>
+    <t>PEDAL 1/2 PLAT ESF NYLON P-667 NITRUS PTO</t>
+  </si>
+  <si>
+    <t>MANOPLA FREERIDE MOOVE VIOLETA 165MM C/ FLANGE</t>
+  </si>
+  <si>
+    <t>DESCANSO 24 ACO LATERAL</t>
+  </si>
+  <si>
+    <t>MOV CENTRAL 40MM EIXO 152MM KENLI (P/ CHAVETA)</t>
+  </si>
+  <si>
+    <t>MANOPLA MIRIM BCO</t>
+  </si>
+  <si>
+    <t>CUBO DT/TR ACO TAIWAN S/ ESP ZINC</t>
+  </si>
+  <si>
+    <t>MANOPLA FREERIDE MOOVE AZUL 165MM C/ FLANGE</t>
+  </si>
+  <si>
+    <t>KIT ACESS P/ BIC 16 TAIWAN PRETO MASC S/RODA</t>
+  </si>
+  <si>
+    <t>KIT ACESS P/ BIC 16 TAIWAN AZUL MASC S/RODA</t>
+  </si>
+  <si>
+    <t>SELIM CAIRU BEACH PU 534 PTO</t>
+  </si>
+  <si>
+    <t>SELIM BEACH SOFT SAFARI 316 KALF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -225,9 +402,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -570,297 +753,553 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="3">
+        <v>7.4054000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="3">
+        <v>6.0833000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="3">
+        <v>36.018000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="3">
+        <v>5.2084000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4.5593000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3">
+        <v>16.459200000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.0541</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="3">
+        <v>25.298400000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7.3786999999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="3">
+        <v>20.294600000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="3">
+        <v>11.976000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.2511999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3.2511999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3.7973000000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="3">
+        <v>9.5250000000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7.9859999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5.8239999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.99199999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3">
+        <v>21.336000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3.7719000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="3">
+        <v>23.113999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="3">
+        <v>22.771100000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="3">
+        <v>8.3185000000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="3">
+        <v>40.017700000000005</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="3">
+        <v>12.9413</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="3">
+        <v>139.15389999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="3">
+        <v>25.273</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="3">
+        <v>146.6977</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="3">
+        <v>32.476399999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2">
-        <v>2.2138999999999998</v>
-      </c>
-      <c r="E2">
-        <v>2.1253439999999997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3">
-        <v>1.9649999999999999</v>
-      </c>
-      <c r="E3">
-        <v>1.8274499999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="3">
+        <v>7.3659999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" s="3">
+        <v>13.703299999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="3">
+        <v>32.476399999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="3">
+        <v>15.064499999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E36" s="3">
+        <v>26.949399999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="3">
+        <v>196.85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4">
-        <v>5.9735999999999994</v>
-      </c>
-      <c r="E4">
-        <v>5.7346559999999993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5">
-        <v>22.008000000000003</v>
-      </c>
-      <c r="E5">
-        <v>20.247360000000004</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B38" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>23.841999999999999</v>
-      </c>
-      <c r="E6">
-        <v>21.934639999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7">
-        <v>19.623799999999999</v>
-      </c>
-      <c r="E7">
-        <v>18.053895999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="E38" s="3">
+        <v>18.9497</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="3">
+        <v>4.3052999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E40" s="3">
+        <v>6.9088000000000003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7.3659999999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8">
-        <v>7.5979999999999999</v>
-      </c>
-      <c r="E8">
-        <v>6.9901599999999995</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9">
-        <v>51.92</v>
-      </c>
-      <c r="E9">
-        <v>49.843200000000003</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10">
-        <v>19.623799999999999</v>
-      </c>
-      <c r="E10">
-        <v>18.053895999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11">
-        <v>41.278100000000002</v>
-      </c>
-      <c r="E11">
-        <v>37.975852000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12">
-        <v>7.5979999999999999</v>
-      </c>
-      <c r="E12">
-        <v>6.9901599999999995</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13">
-        <v>7.5979999999999999</v>
-      </c>
-      <c r="E13">
-        <v>6.9901599999999995</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14">
-        <v>74.997500000000002</v>
-      </c>
-      <c r="E14">
-        <v>68.997700000000009</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15">
-        <v>1138</v>
-      </c>
-      <c r="E15">
-        <v>1115.24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16">
-        <v>15.42</v>
-      </c>
-      <c r="E16">
-        <v>14.9574</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17">
-        <v>16.989999999999998</v>
-      </c>
-      <c r="E17">
-        <v>16.310399999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18">
-        <v>34.06</v>
-      </c>
-      <c r="E18">
-        <v>31.3352</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19">
-        <v>48.59</v>
-      </c>
-      <c r="E19">
-        <v>46.6464</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20">
-        <v>6.99</v>
-      </c>
-      <c r="E20">
-        <v>6.5009700000000006</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21">
-        <v>23.82</v>
-      </c>
-      <c r="E21">
-        <v>22.8672</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22">
-        <v>1.43</v>
-      </c>
-      <c r="E22">
-        <v>1.3871</v>
+      <c r="E42" s="3">
+        <v>7.3659999999999997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3.7719000000000005</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44" s="3">
+        <v>14.427199999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1.4224000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="3">
+        <v>15.748000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>7.3659999999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10.401299999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10.401299999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E50" s="3">
+        <v>34.785299999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E51" s="3">
+        <v>26.809699999999999</v>
       </c>
     </row>
   </sheetData>
